--- a/Docs/ProfitabilityRD.xlsx
+++ b/Docs/ProfitabilityRD.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7313"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7313" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MVP" sheetId="4" r:id="rId1"/>
@@ -1244,392 +1244,392 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="5" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="5" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1934,20 +1934,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="129"/>
     </row>
     <row r="2" spans="2:10" s="2" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
@@ -1965,18 +1965,18 @@
       <c r="G2" s="18">
         <v>46235</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="30">
         <v>46266</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="6">
@@ -1994,14 +1994,14 @@
       <c r="G3" s="6">
         <v>0.25</v>
       </c>
-      <c r="H3" s="42">
+      <c r="H3" s="31">
         <v>0.25</v>
       </c>
-      <c r="I3" s="54">
+      <c r="I3" s="42">
         <f>SUM(E3:H3)*C3*160</f>
         <v>32000</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J3" s="29">
         <v>0</v>
       </c>
     </row>
@@ -2027,8 +2027,8 @@
       <c r="H4" s="14">
         <v>0.25</v>
       </c>
-      <c r="I4" s="57">
-        <f t="shared" ref="I4:J11" si="0">SUM(E4:H4)*C4*160</f>
+      <c r="I4" s="45">
+        <f t="shared" ref="I4:I11" si="0">SUM(E4:H4)*C4*160</f>
         <v>12000</v>
       </c>
       <c r="J4" s="20">
@@ -2057,7 +2057,7 @@
       <c r="H5" s="14">
         <v>0.5</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="45">
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
@@ -2087,7 +2087,7 @@
       <c r="H6" s="14">
         <v>0.5</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="45">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="H7" s="14">
         <v>2</v>
       </c>
-      <c r="I7" s="57">
+      <c r="I7" s="45">
         <f t="shared" si="0"/>
         <v>28000</v>
       </c>
@@ -2147,7 +2147,7 @@
       <c r="H8" s="14">
         <v>2</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="45">
         <f t="shared" si="0"/>
         <v>28000</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="H9" s="14">
         <v>1</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="45">
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
@@ -2207,7 +2207,7 @@
       <c r="H10" s="14">
         <v>1</v>
       </c>
-      <c r="I10" s="57">
+      <c r="I10" s="45">
         <f t="shared" si="0"/>
         <v>16000</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="H11" s="16">
         <v>2</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="50">
         <f t="shared" si="0"/>
         <v>28000</v>
       </c>
@@ -2246,42 +2246,42 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31">
+      <c r="B12" s="125"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="26">
         <f>SUM(E3:E11)</f>
         <v>5.5</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="26">
         <f t="shared" ref="F12:H12" si="1">SUM(F3:F11)</f>
         <v>9.5</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="26">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="32">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="53">
         <f>SUM(I3:I11)</f>
         <v>172000</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="27">
         <f>SUM(J3:J11)</f>
         <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:10" s="2" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="35"/>
+      <c r="C13" s="122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="122"/>
       <c r="E13" s="18">
         <v>46174</v>
       </c>
@@ -2291,22 +2291,22 @@
       <c r="G13" s="18">
         <v>46235</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="30">
         <v>46266</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="33" t="s">
         <v>29</v>
       </c>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="36"/>
+      <c r="C14" s="123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="123"/>
       <c r="E14" s="6">
         <v>50</v>
       </c>
@@ -2316,10 +2316,10 @@
       <c r="G14" s="6">
         <v>50</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="31">
         <v>50</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="34">
         <f>SUM(E14:H14)</f>
         <v>200</v>
       </c>
@@ -2328,10 +2328,10 @@
       <c r="B15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="37"/>
+      <c r="D15" s="124"/>
       <c r="E15" s="8">
         <v>50</v>
       </c>
@@ -2344,98 +2344,98 @@
       <c r="H15" s="16">
         <v>50</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="36">
         <f>SUM(E15:H15)</f>
         <v>200</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="150" t="s">
+      <c r="B16" s="119" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="151"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="31">
-        <v>0</v>
-      </c>
-      <c r="F16" s="31">
-        <v>0</v>
-      </c>
-      <c r="G16" s="31">
-        <v>0</v>
-      </c>
-      <c r="H16" s="43">
-        <v>0</v>
-      </c>
-      <c r="I16" s="52"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="26">
+        <v>0</v>
+      </c>
+      <c r="F16" s="26">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26">
+        <v>0</v>
+      </c>
+      <c r="H16" s="32">
+        <v>0</v>
+      </c>
+      <c r="I16" s="40"/>
     </row>
     <row r="17" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31">
+      <c r="B17" s="125"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="26">
         <f>SUM(E14:E15)</f>
         <v>100</v>
       </c>
-      <c r="F17" s="31">
-        <f t="shared" ref="F17:J17" si="2">SUM(F14:F15)</f>
+      <c r="F17" s="26">
+        <f t="shared" ref="F17:I17" si="2">SUM(F14:F15)</f>
         <v>100</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="26">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="50">
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="38">
         <f>J12+I17</f>
         <v>700</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="20" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="50">
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="38">
         <f>I18/4</f>
         <v>175</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B1:J1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2461,20 +2461,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="129"/>
     </row>
     <row r="2" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
@@ -2492,18 +2492,18 @@
       <c r="G2" s="18">
         <v>46357</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="6">
@@ -2518,14 +2518,14 @@
       <c r="F3" s="6">
         <v>0.25</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="31">
         <v>0.25</v>
       </c>
-      <c r="H3" s="54">
-        <f>SUM(E3:G3)*C3*160</f>
+      <c r="H3" s="42">
+        <f t="shared" ref="H3:H14" si="0">SUM(E3:G3)*C3*160</f>
         <v>24000</v>
       </c>
-      <c r="I3" s="55">
+      <c r="I3" s="43">
         <v>100</v>
       </c>
       <c r="J3" s="11">
@@ -2552,11 +2552,11 @@
       <c r="G4" s="14">
         <v>0.5</v>
       </c>
-      <c r="H4" s="57">
-        <f>SUM(E4:G4)*C4*160</f>
+      <c r="H4" s="45">
+        <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="46">
         <v>90</v>
       </c>
       <c r="J4" s="12">
@@ -2583,15 +2583,15 @@
       <c r="G5" s="14">
         <v>2</v>
       </c>
-      <c r="H5" s="57">
-        <f>SUM(E5:G5)*C5*160</f>
+      <c r="H5" s="45">
+        <f t="shared" si="0"/>
         <v>38400</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5" s="46">
         <v>90</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" ref="J5:J13" si="0">H5*(100-I5)/100</f>
+        <f t="shared" ref="J5:J13" si="1">H5*(100-I5)/100</f>
         <v>3840</v>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="G6" s="14">
         <v>2</v>
       </c>
-      <c r="H6" s="57">
-        <f>SUM(E6:G6)*C6*160</f>
+      <c r="H6" s="45">
+        <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="46">
         <v>100</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2645,15 +2645,15 @@
       <c r="G7" s="14">
         <v>2</v>
       </c>
-      <c r="H7" s="57">
-        <f>SUM(E7:G7)*C7*160</f>
+      <c r="H7" s="45">
+        <f t="shared" si="0"/>
         <v>38400</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="46">
         <v>90</v>
       </c>
       <c r="J7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3840</v>
       </c>
     </row>
@@ -2676,15 +2676,15 @@
       <c r="G8" s="14">
         <v>2</v>
       </c>
-      <c r="H8" s="57">
-        <f>SUM(E8:G8)*C8*160</f>
+      <c r="H8" s="45">
+        <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="46">
         <v>100</v>
       </c>
       <c r="J8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2707,15 +2707,15 @@
       <c r="G9" s="14">
         <v>2</v>
       </c>
-      <c r="H9" s="57">
-        <f>SUM(E9:G9)*C9*160</f>
+      <c r="H9" s="45">
+        <f t="shared" si="0"/>
         <v>38400</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="46">
         <v>90</v>
       </c>
       <c r="J9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3840</v>
       </c>
     </row>
@@ -2738,15 +2738,15 @@
       <c r="G10" s="14">
         <v>2</v>
       </c>
-      <c r="H10" s="57">
-        <f>SUM(E10:G10)*C10*160</f>
+      <c r="H10" s="45">
+        <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="I10" s="58">
+      <c r="I10" s="46">
         <v>100</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2769,15 +2769,15 @@
       <c r="G11" s="14">
         <v>1</v>
       </c>
-      <c r="H11" s="57">
-        <f>SUM(E11:G11)*C11*160</f>
+      <c r="H11" s="45">
+        <f t="shared" si="0"/>
         <v>19200</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="46">
         <v>90</v>
       </c>
       <c r="J11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1920</v>
       </c>
     </row>
@@ -2800,15 +2800,15 @@
       <c r="G12" s="14">
         <v>1</v>
       </c>
-      <c r="H12" s="57">
-        <f>SUM(E12:G12)*C12*160</f>
+      <c r="H12" s="45">
+        <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="I12" s="58">
+      <c r="I12" s="46">
         <v>100</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2831,15 +2831,15 @@
       <c r="G13" s="15">
         <v>2</v>
       </c>
-      <c r="H13" s="59">
-        <f>SUM(E13:G13)*C13*160</f>
+      <c r="H13" s="47">
+        <f t="shared" si="0"/>
         <v>38400</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="48">
         <v>90</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3840</v>
       </c>
     </row>
@@ -2862,11 +2862,11 @@
       <c r="G14" s="16">
         <v>2</v>
       </c>
-      <c r="H14" s="62">
-        <f>SUM(E14:G14)*C14*160</f>
+      <c r="H14" s="50">
+        <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="I14" s="63">
+      <c r="I14" s="51">
         <v>100</v>
       </c>
       <c r="J14" s="13">
@@ -2875,38 +2875,38 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31">
-        <f t="shared" ref="E15:G15" si="1">SUM(E3:E14)</f>
+      <c r="B15" s="125"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="26">
+        <f t="shared" ref="E15:G15" si="2">SUM(E3:E14)</f>
         <v>18.75</v>
       </c>
-      <c r="F15" s="31">
-        <f t="shared" si="1"/>
+      <c r="F15" s="26">
+        <f t="shared" si="2"/>
         <v>18.75</v>
       </c>
-      <c r="G15" s="43">
-        <f t="shared" si="1"/>
+      <c r="G15" s="32">
+        <f t="shared" si="2"/>
         <v>18.75</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="56">
         <f>SUM(H3:H14)</f>
         <v>322800</v>
       </c>
-      <c r="J15" s="67">
+      <c r="J15" s="55">
         <f>SUM(J3:J14)</f>
         <v>19080</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="35"/>
+      <c r="C16" s="122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="122"/>
       <c r="E16" s="18">
         <v>46296</v>
       </c>
@@ -2916,28 +2916,28 @@
       <c r="G16" s="18">
         <v>46357</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="33" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="36"/>
+      <c r="C17" s="123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="123"/>
       <c r="E17" s="6">
         <v>100</v>
       </c>
       <c r="F17" s="6">
         <v>100</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="31">
         <v>100</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="34">
         <f>SUM(E17:G17)</f>
         <v>300</v>
       </c>
@@ -2946,10 +2946,10 @@
       <c r="B18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="24"/>
+      <c r="D18" s="130"/>
       <c r="E18" s="4">
         <v>100</v>
       </c>
@@ -2959,7 +2959,7 @@
       <c r="G18" s="14">
         <v>100</v>
       </c>
-      <c r="H18" s="47">
+      <c r="H18" s="35">
         <f>SUM(E18:G18)</f>
         <v>300</v>
       </c>
@@ -2968,10 +2968,10 @@
       <c r="B19" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="24"/>
+      <c r="C19" s="130" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="130"/>
       <c r="E19" s="4">
         <v>50</v>
       </c>
@@ -2981,7 +2981,7 @@
       <c r="G19" s="14">
         <v>50</v>
       </c>
-      <c r="H19" s="47">
+      <c r="H19" s="35">
         <f>SUM(E19:G19)</f>
         <v>150</v>
       </c>
@@ -2990,10 +2990,10 @@
       <c r="B20" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="37"/>
+      <c r="D20" s="124"/>
       <c r="E20" s="8">
         <v>50</v>
       </c>
@@ -3003,63 +3003,66 @@
       <c r="G20" s="16">
         <v>50</v>
       </c>
-      <c r="H20" s="48">
+      <c r="H20" s="36">
         <f>SUM(E20:G20)</f>
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31">
-        <f t="shared" ref="E21:H21" si="2">SUM(E17:E18)</f>
+      <c r="B21" s="125"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="26">
+        <f t="shared" ref="E21:G21" si="3">SUM(E17:E18)</f>
         <v>200</v>
       </c>
-      <c r="F21" s="31">
-        <f t="shared" si="2"/>
+      <c r="F21" s="26">
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="G21" s="43">
-        <f t="shared" si="2"/>
+      <c r="G21" s="32">
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="H21" s="49">
+      <c r="H21" s="37">
         <f>SUM(H17:H20)</f>
         <v>900</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="66">
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="54">
         <f>J15+H21</f>
         <v>19980</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="24" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="66">
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="54">
         <f>H22/3</f>
         <v>6660</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="C16:D16"/>
@@ -3067,9 +3070,6 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3097,61 +3097,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="84"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="2" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="87">
+      <c r="E2" s="64">
         <v>46388</v>
       </c>
-      <c r="F2" s="87">
+      <c r="F2" s="64">
         <v>46419</v>
       </c>
-      <c r="G2" s="87">
+      <c r="G2" s="64">
         <v>46447</v>
       </c>
-      <c r="H2" s="87">
+      <c r="H2" s="64">
         <v>46478</v>
       </c>
-      <c r="I2" s="87">
+      <c r="I2" s="64">
         <v>46508</v>
       </c>
-      <c r="J2" s="87">
+      <c r="J2" s="64">
         <v>46539</v>
       </c>
-      <c r="K2" s="88" t="s">
+      <c r="K2" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="89" t="s">
+      <c r="L2" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="90" t="s">
+      <c r="M2" s="67" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="6">
@@ -3175,14 +3175,14 @@
       <c r="I3" s="6">
         <v>0.25</v>
       </c>
-      <c r="J3" s="42">
+      <c r="J3" s="31">
         <v>0.25</v>
       </c>
-      <c r="K3" s="54">
+      <c r="K3" s="42">
         <f t="shared" ref="K3:K14" si="0">SUM(E3:J3)*C3*160</f>
         <v>48000</v>
       </c>
-      <c r="L3" s="55">
+      <c r="L3" s="43">
         <v>100</v>
       </c>
       <c r="M3" s="11">
@@ -3218,11 +3218,11 @@
       <c r="J4" s="14">
         <v>0.5</v>
       </c>
-      <c r="K4" s="57">
+      <c r="K4" s="45">
         <f t="shared" si="0"/>
         <v>36000</v>
       </c>
-      <c r="L4" s="58">
+      <c r="L4" s="46">
         <v>90</v>
       </c>
       <c r="M4" s="12">
@@ -3258,11 +3258,11 @@
       <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" s="57">
+      <c r="K5" s="45">
         <f t="shared" si="0"/>
         <v>153600</v>
       </c>
-      <c r="L5" s="58">
+      <c r="L5" s="46">
         <v>90</v>
       </c>
       <c r="M5" s="12">
@@ -3298,11 +3298,11 @@
       <c r="J6" s="4">
         <v>4</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="45">
         <f t="shared" si="0"/>
         <v>96000</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="46">
         <v>100</v>
       </c>
       <c r="M6" s="12">
@@ -3338,11 +3338,11 @@
       <c r="J7" s="4">
         <v>4</v>
       </c>
-      <c r="K7" s="57">
+      <c r="K7" s="45">
         <f t="shared" si="0"/>
         <v>153600</v>
       </c>
-      <c r="L7" s="58">
+      <c r="L7" s="46">
         <v>90</v>
       </c>
       <c r="M7" s="12">
@@ -3378,11 +3378,11 @@
       <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="K8" s="57">
+      <c r="K8" s="45">
         <f t="shared" si="0"/>
         <v>96000</v>
       </c>
-      <c r="L8" s="58">
+      <c r="L8" s="46">
         <v>100</v>
       </c>
       <c r="M8" s="12">
@@ -3418,11 +3418,11 @@
       <c r="J9" s="4">
         <v>4</v>
       </c>
-      <c r="K9" s="57">
+      <c r="K9" s="45">
         <f t="shared" si="0"/>
         <v>153600</v>
       </c>
-      <c r="L9" s="58">
+      <c r="L9" s="46">
         <v>90</v>
       </c>
       <c r="M9" s="12">
@@ -3458,11 +3458,11 @@
       <c r="J10" s="4">
         <v>4</v>
       </c>
-      <c r="K10" s="57">
+      <c r="K10" s="45">
         <f t="shared" si="0"/>
         <v>96000</v>
       </c>
-      <c r="L10" s="58">
+      <c r="L10" s="46">
         <v>100</v>
       </c>
       <c r="M10" s="12">
@@ -3498,11 +3498,11 @@
       <c r="J11" s="4">
         <v>2</v>
       </c>
-      <c r="K11" s="57">
+      <c r="K11" s="45">
         <f t="shared" si="0"/>
         <v>76800</v>
       </c>
-      <c r="L11" s="58">
+      <c r="L11" s="46">
         <v>90</v>
       </c>
       <c r="M11" s="12">
@@ -3538,11 +3538,11 @@
       <c r="J12" s="4">
         <v>2</v>
       </c>
-      <c r="K12" s="57">
+      <c r="K12" s="45">
         <f t="shared" si="0"/>
         <v>48000</v>
       </c>
-      <c r="L12" s="58">
+      <c r="L12" s="46">
         <v>100</v>
       </c>
       <c r="M12" s="12">
@@ -3578,11 +3578,11 @@
       <c r="J13" s="10">
         <v>4</v>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="47">
         <f t="shared" si="0"/>
         <v>153600</v>
       </c>
-      <c r="L13" s="60">
+      <c r="L13" s="48">
         <v>90</v>
       </c>
       <c r="M13" s="12">
@@ -3618,11 +3618,11 @@
       <c r="J14" s="8">
         <v>4</v>
       </c>
-      <c r="K14" s="62">
+      <c r="K14" s="50">
         <f t="shared" si="0"/>
         <v>96000</v>
       </c>
-      <c r="L14" s="63">
+      <c r="L14" s="51">
         <v>100</v>
       </c>
       <c r="M14" s="13">
@@ -3631,80 +3631,80 @@
       </c>
     </row>
     <row r="15" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31">
+      <c r="B15" s="125"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="26">
         <f t="shared" ref="E15:J15" si="2">SUM(E3:E14)</f>
         <v>36.75</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="26">
         <f t="shared" ref="F15:H15" si="3">SUM(F3:F14)</f>
         <v>36.75</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="26">
         <f t="shared" si="3"/>
         <v>36.75</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="26">
         <f t="shared" si="3"/>
         <v>36.75</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="26">
         <f t="shared" si="2"/>
         <v>36.75</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="32">
         <f t="shared" si="2"/>
         <v>36.75</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="68">
         <f>SUM(K3:K14)</f>
         <v>1207200</v>
       </c>
-      <c r="M15" s="92">
+      <c r="M15" s="69">
         <f>SUM(M3:M14)</f>
         <v>72720</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="93"/>
-      <c r="E16" s="87">
+      <c r="C16" s="141" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="141"/>
+      <c r="E16" s="64">
         <v>46388</v>
       </c>
-      <c r="F16" s="87">
+      <c r="F16" s="64">
         <v>46419</v>
       </c>
-      <c r="G16" s="87">
+      <c r="G16" s="64">
         <v>46447</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="64">
         <v>46478</v>
       </c>
-      <c r="I16" s="87">
+      <c r="I16" s="64">
         <v>46508</v>
       </c>
-      <c r="J16" s="87">
+      <c r="J16" s="64">
         <v>46539</v>
       </c>
-      <c r="K16" s="88" t="s">
+      <c r="K16" s="65" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="36"/>
+      <c r="C17" s="123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="123"/>
       <c r="E17" s="6">
         <v>200</v>
       </c>
@@ -3720,10 +3720,10 @@
       <c r="I17" s="6">
         <v>200</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="31">
         <v>200</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="42">
         <f>SUM(E17:J17)</f>
         <v>1200</v>
       </c>
@@ -3732,10 +3732,10 @@
       <c r="B18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="24"/>
+      <c r="D18" s="130"/>
       <c r="E18" s="4">
         <v>200</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="J18" s="14">
         <v>200</v>
       </c>
-      <c r="K18" s="57">
+      <c r="K18" s="45">
         <f>SUM(E18:J18)</f>
         <v>1200</v>
       </c>
@@ -3763,10 +3763,10 @@
       <c r="B19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="24"/>
+      <c r="C19" s="130" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="130"/>
       <c r="E19" s="4">
         <v>500</v>
       </c>
@@ -3785,7 +3785,7 @@
       <c r="J19" s="14">
         <v>500</v>
       </c>
-      <c r="K19" s="57">
+      <c r="K19" s="45">
         <f>SUM(E19:J19)</f>
         <v>3000</v>
       </c>
@@ -3794,10 +3794,10 @@
       <c r="B20" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="37"/>
+      <c r="D20" s="124"/>
       <c r="E20" s="8">
         <v>500</v>
       </c>
@@ -3816,1141 +3816,1141 @@
       <c r="J20" s="16">
         <v>500</v>
       </c>
-      <c r="K20" s="62">
+      <c r="K20" s="50">
         <f>SUM(E20:J20)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="64">
+      <c r="B21" s="125"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="52">
         <f>SUM(E17:E20)</f>
         <v>1400</v>
       </c>
-      <c r="F21" s="64">
+      <c r="F21" s="52">
         <f t="shared" ref="F21:J21" si="4">SUM(F17:F20)</f>
         <v>1400</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G21" s="52">
         <f t="shared" si="4"/>
         <v>1400</v>
       </c>
-      <c r="H21" s="64">
+      <c r="H21" s="52">
         <f t="shared" si="4"/>
         <v>1400</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I21" s="52">
         <f t="shared" si="4"/>
         <v>1400</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J21" s="52">
         <f t="shared" si="4"/>
         <v>1400</v>
       </c>
-      <c r="K21" s="91">
+      <c r="K21" s="68">
         <f>SUM(K17:K20)</f>
         <v>8400</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="97">
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="70">
         <f>M15+K21</f>
         <v>81120</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="24" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="138" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="108"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="108"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="109"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="139"/>
+      <c r="M24" s="140"/>
     </row>
     <row r="25" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25"/>
-      <c r="B25" s="117" t="s">
+      <c r="B25" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="118" t="s">
+      <c r="C25" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="118" t="s">
+      <c r="D25" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="119">
+      <c r="E25" s="89">
         <v>46388</v>
       </c>
-      <c r="F25" s="119">
+      <c r="F25" s="89">
         <v>46419</v>
       </c>
-      <c r="G25" s="119">
+      <c r="G25" s="89">
         <v>46447</v>
       </c>
-      <c r="H25" s="119">
+      <c r="H25" s="89">
         <v>46478</v>
       </c>
-      <c r="I25" s="119">
+      <c r="I25" s="89">
         <v>46508</v>
       </c>
-      <c r="J25" s="119">
+      <c r="J25" s="89">
         <v>46539</v>
       </c>
-      <c r="K25" s="118" t="s">
+      <c r="K25" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="L25" s="118" t="s">
+      <c r="L25" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="M25" s="120" t="s">
+      <c r="M25" s="90" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26"/>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="111">
+      <c r="C26" s="81">
         <v>40</v>
       </c>
-      <c r="D26" s="112" t="s">
+      <c r="D26" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="113">
+      <c r="E26" s="83">
         <v>1</v>
       </c>
-      <c r="F26" s="113">
+      <c r="F26" s="83">
         <v>1</v>
       </c>
-      <c r="G26" s="113">
+      <c r="G26" s="83">
         <v>1</v>
       </c>
-      <c r="H26" s="113">
+      <c r="H26" s="83">
         <v>1</v>
       </c>
-      <c r="I26" s="113">
+      <c r="I26" s="83">
         <v>1</v>
       </c>
-      <c r="J26" s="113">
+      <c r="J26" s="83">
         <v>1</v>
       </c>
-      <c r="K26" s="114">
+      <c r="K26" s="84">
         <f>SUM(E26:J26)*C26*160</f>
         <v>38400</v>
       </c>
-      <c r="L26" s="115">
+      <c r="L26" s="85">
         <v>90</v>
       </c>
-      <c r="M26" s="116">
+      <c r="M26" s="86">
         <f>K26*(1-L26/100)</f>
         <v>3839.9999999999991</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27"/>
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="99">
+      <c r="C27" s="72">
         <v>25</v>
       </c>
-      <c r="D27" s="100" t="s">
+      <c r="D27" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="101">
+      <c r="E27" s="74">
         <v>1</v>
       </c>
-      <c r="F27" s="101">
+      <c r="F27" s="74">
         <v>1</v>
       </c>
-      <c r="G27" s="101">
+      <c r="G27" s="74">
         <v>1</v>
       </c>
-      <c r="H27" s="101">
+      <c r="H27" s="74">
         <v>1</v>
       </c>
-      <c r="I27" s="101">
+      <c r="I27" s="74">
         <v>1</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="74">
         <v>1</v>
       </c>
-      <c r="K27" s="102">
+      <c r="K27" s="75">
         <f>SUM(E27:J27)*C27*160</f>
         <v>24000</v>
       </c>
-      <c r="L27" s="103">
+      <c r="L27" s="76">
         <v>90</v>
       </c>
-      <c r="M27" s="105">
+      <c r="M27" s="78">
         <f>K27*(1-L27/100)</f>
         <v>2399.9999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28"/>
-      <c r="B28" s="104" t="s">
+      <c r="B28" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="99">
+      <c r="C28" s="72">
         <v>25</v>
       </c>
-      <c r="D28" s="100" t="s">
+      <c r="D28" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="101">
+      <c r="E28" s="74">
         <v>1</v>
       </c>
-      <c r="F28" s="101">
+      <c r="F28" s="74">
         <v>1</v>
       </c>
-      <c r="G28" s="101">
+      <c r="G28" s="74">
         <v>1</v>
       </c>
-      <c r="H28" s="101">
+      <c r="H28" s="74">
         <v>1</v>
       </c>
-      <c r="I28" s="101">
+      <c r="I28" s="74">
         <v>1</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="74">
         <v>1</v>
       </c>
-      <c r="K28" s="102">
+      <c r="K28" s="75">
         <f>SUM(E28:J28)*C28*160</f>
         <v>24000</v>
       </c>
-      <c r="L28" s="103">
+      <c r="L28" s="76">
         <v>90</v>
       </c>
-      <c r="M28" s="105">
+      <c r="M28" s="78">
         <f>K28*(1-L28/100)</f>
         <v>2399.9999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29"/>
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="99">
+      <c r="C29" s="72">
         <v>25</v>
       </c>
-      <c r="D29" s="100" t="s">
+      <c r="D29" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="101">
-        <v>0</v>
-      </c>
-      <c r="F29" s="101">
-        <v>0</v>
-      </c>
-      <c r="G29" s="101">
+      <c r="E29" s="74">
+        <v>0</v>
+      </c>
+      <c r="F29" s="74">
+        <v>0</v>
+      </c>
+      <c r="G29" s="74">
         <v>0.5</v>
       </c>
-      <c r="H29" s="101">
+      <c r="H29" s="74">
         <v>0.5</v>
       </c>
-      <c r="I29" s="101">
+      <c r="I29" s="74">
         <v>0.5</v>
       </c>
-      <c r="J29" s="101">
+      <c r="J29" s="74">
         <v>0.5</v>
       </c>
-      <c r="K29" s="102">
+      <c r="K29" s="75">
         <f>SUM(E29:J29)*C29*160</f>
         <v>8000</v>
       </c>
-      <c r="L29" s="103">
+      <c r="L29" s="76">
         <v>90</v>
       </c>
-      <c r="M29" s="105">
+      <c r="M29" s="78">
         <f>K29*(1-L29/100)</f>
         <v>799.99999999999977</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30"/>
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="122">
+      <c r="C30" s="92">
         <v>25</v>
       </c>
-      <c r="D30" s="123" t="s">
+      <c r="D30" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="124">
-        <v>0</v>
-      </c>
-      <c r="F30" s="124">
-        <v>0</v>
-      </c>
-      <c r="G30" s="124">
+      <c r="E30" s="94">
+        <v>0</v>
+      </c>
+      <c r="F30" s="94">
+        <v>0</v>
+      </c>
+      <c r="G30" s="94">
         <v>0.5</v>
       </c>
-      <c r="H30" s="124">
+      <c r="H30" s="94">
         <v>0.5</v>
       </c>
-      <c r="I30" s="124">
+      <c r="I30" s="94">
         <v>0.5</v>
       </c>
-      <c r="J30" s="124">
+      <c r="J30" s="94">
         <v>0.5</v>
       </c>
-      <c r="K30" s="125">
+      <c r="K30" s="95">
         <f>SUM(E30:J30)*C30*160</f>
         <v>8000</v>
       </c>
-      <c r="L30" s="126">
+      <c r="L30" s="96">
         <v>90</v>
       </c>
-      <c r="M30" s="127">
+      <c r="M30" s="97">
         <f>K30*(1-L30/100)</f>
         <v>799.99999999999977</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31"/>
-      <c r="B31" s="129" t="s">
+      <c r="B31" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="130"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="133">
+      <c r="C31" s="100"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="102"/>
+      <c r="K31" s="103">
         <f>SUM(K26:K30)</f>
         <v>102400</v>
       </c>
-      <c r="L31" s="134"/>
-      <c r="M31" s="135">
+      <c r="L31" s="104"/>
+      <c r="M31" s="105">
         <f>SUM(M26:M30)</f>
         <v>10239.999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32"/>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="128" t="s">
+      <c r="C32" s="81"/>
+      <c r="D32" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="E32" s="113">
-        <v>0</v>
-      </c>
-      <c r="F32" s="113">
-        <v>0</v>
-      </c>
-      <c r="G32" s="113">
+      <c r="E32" s="83">
+        <v>0</v>
+      </c>
+      <c r="F32" s="83">
+        <v>0</v>
+      </c>
+      <c r="G32" s="83">
         <v>250</v>
       </c>
-      <c r="H32" s="113">
+      <c r="H32" s="83">
         <v>250</v>
       </c>
-      <c r="I32" s="113">
+      <c r="I32" s="83">
         <v>750</v>
       </c>
-      <c r="J32" s="113">
+      <c r="J32" s="83">
         <v>750</v>
       </c>
-      <c r="K32" s="114">
+      <c r="K32" s="84">
         <f t="shared" ref="K32:K37" si="5">SUM(E32:J32)</f>
         <v>2000</v>
       </c>
-      <c r="L32" s="115">
-        <v>0</v>
-      </c>
-      <c r="M32" s="116">
+      <c r="L32" s="85">
+        <v>0</v>
+      </c>
+      <c r="M32" s="86">
         <f t="shared" ref="M32:M37" si="6">K32*(1-L32/100)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33"/>
-      <c r="B33" s="106" t="s">
+      <c r="B33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="99"/>
-      <c r="D33" s="98" t="s">
+      <c r="C33" s="72"/>
+      <c r="D33" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="101">
-        <v>0</v>
-      </c>
-      <c r="F33" s="101">
-        <v>0</v>
-      </c>
-      <c r="G33" s="101">
+      <c r="E33" s="74">
+        <v>0</v>
+      </c>
+      <c r="F33" s="74">
+        <v>0</v>
+      </c>
+      <c r="G33" s="74">
         <v>200</v>
       </c>
-      <c r="H33" s="101">
+      <c r="H33" s="74">
         <v>200</v>
       </c>
-      <c r="I33" s="101">
+      <c r="I33" s="74">
         <v>600</v>
       </c>
-      <c r="J33" s="101">
+      <c r="J33" s="74">
         <v>600</v>
       </c>
-      <c r="K33" s="102">
+      <c r="K33" s="75">
         <f t="shared" si="5"/>
         <v>1600</v>
       </c>
-      <c r="L33" s="103">
-        <v>0</v>
-      </c>
-      <c r="M33" s="105">
+      <c r="L33" s="76">
+        <v>0</v>
+      </c>
+      <c r="M33" s="78">
         <f t="shared" si="6"/>
         <v>1600</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34"/>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="99"/>
-      <c r="D34" s="98" t="s">
+      <c r="C34" s="72"/>
+      <c r="D34" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="101">
-        <v>0</v>
-      </c>
-      <c r="F34" s="101">
-        <v>0</v>
-      </c>
-      <c r="G34" s="101">
+      <c r="E34" s="74">
+        <v>0</v>
+      </c>
+      <c r="F34" s="74">
+        <v>0</v>
+      </c>
+      <c r="G34" s="74">
         <v>100</v>
       </c>
-      <c r="H34" s="101">
+      <c r="H34" s="74">
         <v>100</v>
       </c>
-      <c r="I34" s="101">
+      <c r="I34" s="74">
         <v>500</v>
       </c>
-      <c r="J34" s="101">
+      <c r="J34" s="74">
         <v>500</v>
       </c>
-      <c r="K34" s="102">
+      <c r="K34" s="75">
         <f t="shared" si="5"/>
         <v>1200</v>
       </c>
-      <c r="L34" s="103">
-        <v>0</v>
-      </c>
-      <c r="M34" s="105">
+      <c r="L34" s="76">
+        <v>0</v>
+      </c>
+      <c r="M34" s="78">
         <f t="shared" si="6"/>
         <v>1200</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35"/>
-      <c r="B35" s="104" t="s">
+      <c r="B35" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="99"/>
-      <c r="D35" s="98" t="s">
+      <c r="C35" s="72"/>
+      <c r="D35" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="101">
-        <v>0</v>
-      </c>
-      <c r="F35" s="101">
-        <v>0</v>
-      </c>
-      <c r="G35" s="101">
-        <v>0</v>
-      </c>
-      <c r="H35" s="101">
-        <v>0</v>
-      </c>
-      <c r="I35" s="101">
+      <c r="E35" s="74">
+        <v>0</v>
+      </c>
+      <c r="F35" s="74">
+        <v>0</v>
+      </c>
+      <c r="G35" s="74">
+        <v>0</v>
+      </c>
+      <c r="H35" s="74">
+        <v>0</v>
+      </c>
+      <c r="I35" s="74">
         <v>400</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="74">
         <v>400</v>
       </c>
-      <c r="K35" s="102">
+      <c r="K35" s="75">
         <f t="shared" si="5"/>
         <v>800</v>
       </c>
-      <c r="L35" s="103">
-        <v>0</v>
-      </c>
-      <c r="M35" s="105">
+      <c r="L35" s="76">
+        <v>0</v>
+      </c>
+      <c r="M35" s="78">
         <f t="shared" si="6"/>
         <v>800</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36"/>
-      <c r="B36" s="106" t="s">
+      <c r="B36" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="99"/>
-      <c r="D36" s="100" t="s">
+      <c r="C36" s="72"/>
+      <c r="D36" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="101">
+      <c r="E36" s="74">
         <v>50</v>
       </c>
-      <c r="F36" s="101">
+      <c r="F36" s="74">
         <v>50</v>
       </c>
-      <c r="G36" s="101">
+      <c r="G36" s="74">
         <v>100</v>
       </c>
-      <c r="H36" s="101">
+      <c r="H36" s="74">
         <v>100</v>
       </c>
-      <c r="I36" s="101">
+      <c r="I36" s="74">
         <v>200</v>
       </c>
-      <c r="J36" s="101">
+      <c r="J36" s="74">
         <v>200</v>
       </c>
-      <c r="K36" s="102">
+      <c r="K36" s="75">
         <f t="shared" si="5"/>
         <v>700</v>
       </c>
-      <c r="L36" s="103">
-        <v>0</v>
-      </c>
-      <c r="M36" s="105">
+      <c r="L36" s="76">
+        <v>0</v>
+      </c>
+      <c r="M36" s="78">
         <f t="shared" si="6"/>
         <v>700</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37"/>
-      <c r="B37" s="121" t="s">
+      <c r="B37" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="122"/>
-      <c r="D37" s="136" t="s">
+      <c r="C37" s="92"/>
+      <c r="D37" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="E37" s="124">
-        <v>0</v>
-      </c>
-      <c r="F37" s="124">
-        <v>0</v>
-      </c>
-      <c r="G37" s="124">
+      <c r="E37" s="94">
+        <v>0</v>
+      </c>
+      <c r="F37" s="94">
+        <v>0</v>
+      </c>
+      <c r="G37" s="94">
         <v>300</v>
       </c>
-      <c r="H37" s="124">
+      <c r="H37" s="94">
         <v>300</v>
       </c>
-      <c r="I37" s="124">
+      <c r="I37" s="94">
         <v>1500</v>
       </c>
-      <c r="J37" s="124">
+      <c r="J37" s="94">
         <v>1500</v>
       </c>
-      <c r="K37" s="125">
+      <c r="K37" s="95">
         <f t="shared" si="5"/>
         <v>3600</v>
       </c>
-      <c r="L37" s="126">
-        <v>0</v>
-      </c>
-      <c r="M37" s="127">
+      <c r="L37" s="96">
+        <v>0</v>
+      </c>
+      <c r="M37" s="97">
         <f t="shared" si="6"/>
         <v>3600</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38"/>
-      <c r="B38" s="129" t="s">
+      <c r="B38" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="130"/>
-      <c r="D38" s="131"/>
-      <c r="E38" s="132"/>
-      <c r="F38" s="132"/>
-      <c r="G38" s="132"/>
-      <c r="H38" s="132"/>
-      <c r="I38" s="132"/>
-      <c r="J38" s="132"/>
-      <c r="K38" s="133">
+      <c r="C38" s="100"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="103">
         <f>SUM(K32:K37)</f>
         <v>9900</v>
       </c>
-      <c r="L38" s="134"/>
-      <c r="M38" s="135">
+      <c r="L38" s="104"/>
+      <c r="M38" s="105">
         <f>SUM(M32:M37)</f>
         <v>9900</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39"/>
-      <c r="B39" s="110" t="s">
+      <c r="B39" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="111"/>
-      <c r="D39" s="128" t="s">
+      <c r="C39" s="81"/>
+      <c r="D39" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="E39" s="113">
+      <c r="E39" s="83">
         <v>25</v>
       </c>
-      <c r="F39" s="113">
+      <c r="F39" s="83">
         <v>25</v>
       </c>
-      <c r="G39" s="113">
+      <c r="G39" s="83">
         <v>25</v>
       </c>
-      <c r="H39" s="113">
+      <c r="H39" s="83">
         <v>25</v>
       </c>
-      <c r="I39" s="113">
+      <c r="I39" s="83">
         <v>25</v>
       </c>
-      <c r="J39" s="113">
+      <c r="J39" s="83">
         <v>25</v>
       </c>
-      <c r="K39" s="114">
+      <c r="K39" s="84">
         <f>SUM(E39:J39)</f>
         <v>150</v>
       </c>
-      <c r="L39" s="115">
-        <v>0</v>
-      </c>
-      <c r="M39" s="116">
+      <c r="L39" s="85">
+        <v>0</v>
+      </c>
+      <c r="M39" s="86">
         <f>K39*(1-L39/100)</f>
         <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40"/>
-      <c r="B40" s="106" t="s">
+      <c r="B40" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="99"/>
-      <c r="D40" s="98" t="s">
+      <c r="C40" s="72"/>
+      <c r="D40" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="E40" s="101">
+      <c r="E40" s="74">
         <v>20</v>
       </c>
-      <c r="F40" s="101">
+      <c r="F40" s="74">
         <v>20</v>
       </c>
-      <c r="G40" s="101">
+      <c r="G40" s="74">
         <v>20</v>
       </c>
-      <c r="H40" s="101">
+      <c r="H40" s="74">
         <v>20</v>
       </c>
-      <c r="I40" s="101">
+      <c r="I40" s="74">
         <v>20</v>
       </c>
-      <c r="J40" s="101">
+      <c r="J40" s="74">
         <v>20</v>
       </c>
-      <c r="K40" s="102">
+      <c r="K40" s="75">
         <f>SUM(E40:J40)</f>
         <v>120</v>
       </c>
-      <c r="L40" s="103">
-        <v>0</v>
-      </c>
-      <c r="M40" s="105">
+      <c r="L40" s="76">
+        <v>0</v>
+      </c>
+      <c r="M40" s="78">
         <f>K40*(1-L40/100)</f>
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41"/>
-      <c r="B41" s="106" t="s">
+      <c r="B41" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="99"/>
-      <c r="D41" s="98" t="s">
+      <c r="C41" s="72"/>
+      <c r="D41" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="E41" s="101">
+      <c r="E41" s="74">
         <v>30</v>
       </c>
-      <c r="F41" s="101">
+      <c r="F41" s="74">
         <v>30</v>
       </c>
-      <c r="G41" s="101">
+      <c r="G41" s="74">
         <v>30</v>
       </c>
-      <c r="H41" s="101">
+      <c r="H41" s="74">
         <v>30</v>
       </c>
-      <c r="I41" s="101">
+      <c r="I41" s="74">
         <v>30</v>
       </c>
-      <c r="J41" s="101">
+      <c r="J41" s="74">
         <v>30</v>
       </c>
-      <c r="K41" s="102">
+      <c r="K41" s="75">
         <f>SUM(E41:J41)</f>
         <v>180</v>
       </c>
-      <c r="L41" s="103">
-        <v>0</v>
-      </c>
-      <c r="M41" s="105">
+      <c r="L41" s="76">
+        <v>0</v>
+      </c>
+      <c r="M41" s="78">
         <f>K41*(1-L41/100)</f>
         <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42"/>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="122"/>
-      <c r="D42" s="136" t="s">
+      <c r="C42" s="92"/>
+      <c r="D42" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E42" s="124">
+      <c r="E42" s="94">
         <v>50</v>
       </c>
-      <c r="F42" s="124">
+      <c r="F42" s="94">
         <v>50</v>
       </c>
-      <c r="G42" s="124">
+      <c r="G42" s="94">
         <v>50</v>
       </c>
-      <c r="H42" s="124">
+      <c r="H42" s="94">
         <v>50</v>
       </c>
-      <c r="I42" s="124">
+      <c r="I42" s="94">
         <v>50</v>
       </c>
-      <c r="J42" s="124">
+      <c r="J42" s="94">
         <v>50</v>
       </c>
-      <c r="K42" s="125">
+      <c r="K42" s="95">
         <f>SUM(E42:J42)</f>
         <v>300</v>
       </c>
-      <c r="L42" s="126">
-        <v>0</v>
-      </c>
-      <c r="M42" s="127">
+      <c r="L42" s="96">
+        <v>0</v>
+      </c>
+      <c r="M42" s="97">
         <f>K42*(1-L42/100)</f>
         <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43"/>
-      <c r="B43" s="129" t="s">
+      <c r="B43" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="130"/>
-      <c r="D43" s="131"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="133">
+      <c r="C43" s="100"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="102"/>
+      <c r="F43" s="102"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="103">
         <f>SUM(K39:K42)</f>
         <v>750</v>
       </c>
-      <c r="L43" s="134"/>
-      <c r="M43" s="135">
+      <c r="L43" s="104"/>
+      <c r="M43" s="105">
         <f>SUM(M39:M42)</f>
         <v>750</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44"/>
-      <c r="B44" s="138" t="s">
+      <c r="B44" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="111">
+      <c r="C44" s="81">
         <v>15</v>
       </c>
-      <c r="D44" s="112" t="s">
+      <c r="D44" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="113">
+      <c r="E44" s="83">
         <v>0.5</v>
       </c>
-      <c r="F44" s="113">
+      <c r="F44" s="83">
         <v>0.5</v>
       </c>
-      <c r="G44" s="113">
+      <c r="G44" s="83">
         <v>0.5</v>
       </c>
-      <c r="H44" s="113">
+      <c r="H44" s="83">
         <v>0.5</v>
       </c>
-      <c r="I44" s="113">
+      <c r="I44" s="83">
         <v>0.5</v>
       </c>
-      <c r="J44" s="113">
+      <c r="J44" s="83">
         <v>0.5</v>
       </c>
-      <c r="K44" s="114">
+      <c r="K44" s="84">
         <f>SUM(E44:J44)*C44*160</f>
         <v>7200</v>
       </c>
-      <c r="L44" s="115">
+      <c r="L44" s="85">
         <v>90</v>
       </c>
-      <c r="M44" s="116">
+      <c r="M44" s="86">
         <f t="shared" ref="M44:M51" si="7">K44*(1-L44/100)</f>
         <v>719.99999999999989</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45"/>
-      <c r="B45" s="106" t="s">
+      <c r="B45" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="99">
+      <c r="C45" s="72">
         <v>20</v>
       </c>
-      <c r="D45" s="100" t="s">
+      <c r="D45" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="E45" s="101">
+      <c r="E45" s="74">
         <v>0.5</v>
       </c>
-      <c r="F45" s="101">
+      <c r="F45" s="74">
         <v>0.5</v>
       </c>
-      <c r="G45" s="101">
+      <c r="G45" s="74">
         <v>0.5</v>
       </c>
-      <c r="H45" s="101">
+      <c r="H45" s="74">
         <v>0.5</v>
       </c>
-      <c r="I45" s="101">
+      <c r="I45" s="74">
         <v>0.5</v>
       </c>
-      <c r="J45" s="101">
+      <c r="J45" s="74">
         <v>0.5</v>
       </c>
-      <c r="K45" s="102">
+      <c r="K45" s="75">
         <f>SUM(E45:J45)*C45*160</f>
         <v>9600</v>
       </c>
-      <c r="L45" s="103">
+      <c r="L45" s="76">
         <v>90</v>
       </c>
-      <c r="M45" s="105">
+      <c r="M45" s="78">
         <f t="shared" si="7"/>
         <v>959.99999999999977</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46"/>
-      <c r="B46" s="104" t="s">
+      <c r="B46" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="99"/>
-      <c r="D46" s="100" t="s">
+      <c r="C46" s="72"/>
+      <c r="D46" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="E46" s="101">
+      <c r="E46" s="74">
         <v>4500</v>
       </c>
-      <c r="F46" s="101">
-        <v>0</v>
-      </c>
-      <c r="G46" s="101">
-        <v>0</v>
-      </c>
-      <c r="H46" s="101">
-        <v>0</v>
-      </c>
-      <c r="I46" s="101">
-        <v>0</v>
-      </c>
-      <c r="J46" s="101">
-        <v>0</v>
-      </c>
-      <c r="K46" s="102">
+      <c r="F46" s="74">
+        <v>0</v>
+      </c>
+      <c r="G46" s="74">
+        <v>0</v>
+      </c>
+      <c r="H46" s="74">
+        <v>0</v>
+      </c>
+      <c r="I46" s="74">
+        <v>0</v>
+      </c>
+      <c r="J46" s="74">
+        <v>0</v>
+      </c>
+      <c r="K46" s="75">
         <f>SUM(E46:J46)</f>
         <v>4500</v>
       </c>
-      <c r="L46" s="103">
-        <v>0</v>
-      </c>
-      <c r="M46" s="105">
+      <c r="L46" s="76">
+        <v>0</v>
+      </c>
+      <c r="M46" s="78">
         <f t="shared" si="7"/>
         <v>4500</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47"/>
-      <c r="B47" s="104" t="s">
+      <c r="B47" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="99"/>
-      <c r="D47" s="98" t="s">
+      <c r="C47" s="72"/>
+      <c r="D47" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="E47" s="101">
+      <c r="E47" s="74">
         <v>200</v>
       </c>
-      <c r="F47" s="101">
+      <c r="F47" s="74">
         <v>200</v>
       </c>
-      <c r="G47" s="101">
+      <c r="G47" s="74">
         <v>200</v>
       </c>
-      <c r="H47" s="101">
+      <c r="H47" s="74">
         <v>200</v>
       </c>
-      <c r="I47" s="101">
+      <c r="I47" s="74">
         <v>200</v>
       </c>
-      <c r="J47" s="101">
+      <c r="J47" s="74">
         <v>200</v>
       </c>
-      <c r="K47" s="102">
+      <c r="K47" s="75">
         <f>SUM(E47:J47)</f>
         <v>1200</v>
       </c>
-      <c r="L47" s="103">
-        <v>0</v>
-      </c>
-      <c r="M47" s="105">
+      <c r="L47" s="76">
+        <v>0</v>
+      </c>
+      <c r="M47" s="78">
         <f t="shared" si="7"/>
         <v>1200</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48"/>
-      <c r="B48" s="106" t="s">
+      <c r="B48" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="99"/>
-      <c r="D48" s="100" t="s">
+      <c r="C48" s="72"/>
+      <c r="D48" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="E48" s="101">
-        <v>0</v>
-      </c>
-      <c r="F48" s="101">
-        <v>0</v>
-      </c>
-      <c r="G48" s="101">
-        <v>0</v>
-      </c>
-      <c r="H48" s="101">
+      <c r="E48" s="74">
+        <v>0</v>
+      </c>
+      <c r="F48" s="74">
+        <v>0</v>
+      </c>
+      <c r="G48" s="74">
+        <v>0</v>
+      </c>
+      <c r="H48" s="74">
         <v>750</v>
       </c>
-      <c r="I48" s="101">
+      <c r="I48" s="74">
         <v>750</v>
       </c>
-      <c r="J48" s="101">
+      <c r="J48" s="74">
         <v>750</v>
       </c>
-      <c r="K48" s="102">
+      <c r="K48" s="75">
         <f>SUM(E48:J48)</f>
         <v>2250</v>
       </c>
-      <c r="L48" s="103">
-        <v>0</v>
-      </c>
-      <c r="M48" s="105">
+      <c r="L48" s="76">
+        <v>0</v>
+      </c>
+      <c r="M48" s="78">
         <f t="shared" si="7"/>
         <v>2250</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49"/>
-      <c r="B49" s="106" t="s">
+      <c r="B49" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="99">
+      <c r="C49" s="72">
         <v>80</v>
       </c>
-      <c r="D49" s="100" t="s">
+      <c r="D49" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="101">
+      <c r="E49" s="74">
         <v>0.1</v>
       </c>
-      <c r="F49" s="101">
+      <c r="F49" s="74">
         <v>0.1</v>
       </c>
-      <c r="G49" s="101">
+      <c r="G49" s="74">
         <v>0.1</v>
       </c>
-      <c r="H49" s="101">
+      <c r="H49" s="74">
         <v>0.1</v>
       </c>
-      <c r="I49" s="101">
+      <c r="I49" s="74">
         <v>0.1</v>
       </c>
-      <c r="J49" s="101">
+      <c r="J49" s="74">
         <v>0.1</v>
       </c>
-      <c r="K49" s="102">
+      <c r="K49" s="75">
         <f>SUM(E49:J49)*C49*160</f>
         <v>7680</v>
       </c>
-      <c r="L49" s="103">
+      <c r="L49" s="76">
         <v>50</v>
       </c>
-      <c r="M49" s="105">
+      <c r="M49" s="78">
         <f t="shared" si="7"/>
         <v>3840</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50"/>
-      <c r="B50" s="106" t="s">
+      <c r="B50" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="99"/>
-      <c r="D50" s="98" t="s">
+      <c r="C50" s="72"/>
+      <c r="D50" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="E50" s="101">
+      <c r="E50" s="74">
         <v>200</v>
       </c>
-      <c r="F50" s="101">
-        <v>0</v>
-      </c>
-      <c r="G50" s="101">
-        <v>0</v>
-      </c>
-      <c r="H50" s="101">
-        <v>0</v>
-      </c>
-      <c r="I50" s="101">
-        <v>0</v>
-      </c>
-      <c r="J50" s="101">
-        <v>0</v>
-      </c>
-      <c r="K50" s="102">
+      <c r="F50" s="74">
+        <v>0</v>
+      </c>
+      <c r="G50" s="74">
+        <v>0</v>
+      </c>
+      <c r="H50" s="74">
+        <v>0</v>
+      </c>
+      <c r="I50" s="74">
+        <v>0</v>
+      </c>
+      <c r="J50" s="74">
+        <v>0</v>
+      </c>
+      <c r="K50" s="75">
         <f>SUM(E50:J50)</f>
         <v>200</v>
       </c>
-      <c r="L50" s="103">
-        <v>0</v>
-      </c>
-      <c r="M50" s="105">
+      <c r="L50" s="76">
+        <v>0</v>
+      </c>
+      <c r="M50" s="78">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51"/>
-      <c r="B51" s="121" t="s">
+      <c r="B51" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="122"/>
-      <c r="D51" s="136" t="s">
+      <c r="C51" s="92"/>
+      <c r="D51" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="E51" s="124">
+      <c r="E51" s="94">
         <v>150</v>
       </c>
-      <c r="F51" s="124">
+      <c r="F51" s="94">
         <v>150</v>
       </c>
-      <c r="G51" s="124">
+      <c r="G51" s="94">
         <v>150</v>
       </c>
-      <c r="H51" s="124">
+      <c r="H51" s="94">
         <v>150</v>
       </c>
-      <c r="I51" s="124">
+      <c r="I51" s="94">
         <v>150</v>
       </c>
-      <c r="J51" s="124">
+      <c r="J51" s="94">
         <v>150</v>
       </c>
-      <c r="K51" s="125">
+      <c r="K51" s="95">
         <f>SUM(E51:J51)</f>
         <v>900</v>
       </c>
-      <c r="L51" s="126">
-        <v>0</v>
-      </c>
-      <c r="M51" s="127">
+      <c r="L51" s="96">
+        <v>0</v>
+      </c>
+      <c r="M51" s="97">
         <f t="shared" si="7"/>
         <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52"/>
-      <c r="B52" s="129" t="s">
+      <c r="B52" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="130"/>
-      <c r="D52" s="131"/>
-      <c r="E52" s="132"/>
-      <c r="F52" s="132"/>
-      <c r="G52" s="132"/>
-      <c r="H52" s="132"/>
-      <c r="I52" s="132"/>
-      <c r="J52" s="132"/>
-      <c r="K52" s="133">
+      <c r="C52" s="100"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="102"/>
+      <c r="F52" s="102"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="102"/>
+      <c r="J52" s="102"/>
+      <c r="K52" s="103">
         <f>SUM(K44:K51)</f>
         <v>33530</v>
       </c>
-      <c r="L52" s="134"/>
-      <c r="M52" s="135">
+      <c r="L52" s="104"/>
+      <c r="M52" s="105">
         <f>SUM(M44:M51)</f>
         <v>14570</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53"/>
-      <c r="B53" s="139" t="s">
+      <c r="B53" s="109" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="140"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="142"/>
-      <c r="F53" s="142"/>
-      <c r="G53" s="142"/>
-      <c r="H53" s="142"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="142"/>
-      <c r="K53" s="143">
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="112"/>
+      <c r="H53" s="112"/>
+      <c r="I53" s="112"/>
+      <c r="J53" s="112"/>
+      <c r="K53" s="113">
         <f>SUM(K31,K38,K43,K52)</f>
         <v>146580</v>
       </c>
-      <c r="L53" s="144"/>
-      <c r="M53" s="145">
+      <c r="L53" s="114"/>
+      <c r="M53" s="115">
         <f>SUM(M31,M38,M43,M52)</f>
         <v>35460</v>
       </c>
@@ -4973,59 +4973,59 @@
     </row>
     <row r="55" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55"/>
-      <c r="B55" s="139" t="s">
+      <c r="B55" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="140"/>
-      <c r="D55" s="141" t="s">
+      <c r="C55" s="110"/>
+      <c r="D55" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="E55" s="147"/>
-      <c r="F55" s="148"/>
-      <c r="G55" s="148"/>
-      <c r="H55" s="148"/>
-      <c r="I55" s="148"/>
-      <c r="J55" s="149"/>
-      <c r="K55" s="143">
+      <c r="E55" s="132"/>
+      <c r="F55" s="133"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="133"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="134"/>
+      <c r="K55" s="113">
         <f>K22+M53</f>
         <v>116580</v>
       </c>
-      <c r="L55" s="144"/>
-      <c r="M55" s="145">
+      <c r="L55" s="114"/>
+      <c r="M55" s="115">
         <f>K22+M53</f>
         <v>116580</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B57" s="146" t="s">
+      <c r="B57" s="131" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="146"/>
-      <c r="D57" s="146"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="146"/>
-      <c r="G57" s="146"/>
-      <c r="H57" s="146"/>
-      <c r="I57" s="146"/>
-      <c r="J57" s="146"/>
-      <c r="K57" s="146"/>
-      <c r="L57" s="146"/>
-      <c r="M57" s="146"/>
+      <c r="C57" s="131"/>
+      <c r="D57" s="131"/>
+      <c r="E57" s="131"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="131"/>
+      <c r="H57" s="131"/>
+      <c r="I57" s="131"/>
+      <c r="J57" s="131"/>
+      <c r="K57" s="131"/>
+      <c r="L57" s="131"/>
+      <c r="M57" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="B57:M57"/>
     <mergeCell ref="E55:J55"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B24:M24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5053,23 +5053,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="127" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
@@ -5096,18 +5096,18 @@
       <c r="J2" s="18">
         <v>46722</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="6">
@@ -5131,14 +5131,14 @@
       <c r="I3" s="6">
         <v>1</v>
       </c>
-      <c r="J3" s="42">
+      <c r="J3" s="31">
         <v>1</v>
       </c>
-      <c r="K3" s="54">
-        <f>SUM(E3:J3)*C3*160</f>
+      <c r="K3" s="42">
+        <f t="shared" ref="K3:K15" si="0">SUM(E3:J3)*C3*160</f>
         <v>192000</v>
       </c>
-      <c r="L3" s="55">
+      <c r="L3" s="43">
         <v>80</v>
       </c>
       <c r="M3" s="11">
@@ -5174,11 +5174,11 @@
       <c r="J4" s="14">
         <v>2</v>
       </c>
-      <c r="K4" s="57">
-        <f>SUM(E4:J4)*C4*160</f>
+      <c r="K4" s="45">
+        <f t="shared" si="0"/>
         <v>192000</v>
       </c>
-      <c r="L4" s="58">
+      <c r="L4" s="46">
         <v>80</v>
       </c>
       <c r="M4" s="12">
@@ -5214,15 +5214,15 @@
       <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" s="57">
-        <f>SUM(E5:J5)*C5*160</f>
+      <c r="K5" s="45">
+        <f t="shared" si="0"/>
         <v>211200</v>
       </c>
-      <c r="L5" s="58">
+      <c r="L5" s="46">
         <v>80</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ref="M5:M14" si="0">K5*(100-L5)/100</f>
+        <f t="shared" ref="M5:M14" si="1">K5*(100-L5)/100</f>
         <v>42240</v>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="J6" s="4">
         <v>2</v>
       </c>
-      <c r="K6" s="57">
-        <f>SUM(E6:J6)*C6*160</f>
+      <c r="K6" s="45">
+        <f t="shared" si="0"/>
         <v>76800</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="46">
         <v>80</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15360</v>
       </c>
     </row>
@@ -5294,15 +5294,15 @@
       <c r="J7" s="4">
         <v>8</v>
       </c>
-      <c r="K7" s="57">
-        <f>SUM(E7:J7)*C7*160</f>
+      <c r="K7" s="45">
+        <f t="shared" si="0"/>
         <v>403200</v>
       </c>
-      <c r="L7" s="58">
+      <c r="L7" s="46">
         <v>80</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80640</v>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="J8" s="4">
         <v>6</v>
       </c>
-      <c r="K8" s="57">
-        <f>SUM(E8:J8)*C8*160</f>
+      <c r="K8" s="45">
+        <f t="shared" si="0"/>
         <v>192000</v>
       </c>
-      <c r="L8" s="58">
+      <c r="L8" s="46">
         <v>80</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38400</v>
       </c>
     </row>
@@ -5374,15 +5374,15 @@
       <c r="J9" s="4">
         <v>6</v>
       </c>
-      <c r="K9" s="57">
-        <f>SUM(E9:J9)*C9*160</f>
+      <c r="K9" s="45">
+        <f t="shared" si="0"/>
         <v>288000</v>
       </c>
-      <c r="L9" s="58">
+      <c r="L9" s="46">
         <v>80</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57600</v>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="J10" s="4">
         <v>5</v>
       </c>
-      <c r="K10" s="57">
-        <f>SUM(E10:J10)*C10*160</f>
+      <c r="K10" s="45">
+        <f t="shared" si="0"/>
         <v>153600</v>
       </c>
-      <c r="L10" s="58">
+      <c r="L10" s="46">
         <v>80</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30720</v>
       </c>
     </row>
@@ -5454,15 +5454,15 @@
       <c r="J11" s="4">
         <v>4</v>
       </c>
-      <c r="K11" s="57">
-        <f>SUM(E11:J11)*C11*160</f>
+      <c r="K11" s="45">
+        <f t="shared" si="0"/>
         <v>172800</v>
       </c>
-      <c r="L11" s="58">
+      <c r="L11" s="46">
         <v>80</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34560</v>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="J12" s="4">
         <v>2</v>
       </c>
-      <c r="K12" s="57">
-        <f>SUM(E12:J12)*C12*160</f>
+      <c r="K12" s="45">
+        <f t="shared" si="0"/>
         <v>76800</v>
       </c>
-      <c r="L12" s="58">
+      <c r="L12" s="46">
         <v>80</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15360</v>
       </c>
     </row>
@@ -5534,15 +5534,15 @@
       <c r="J13" s="10">
         <v>6</v>
       </c>
-      <c r="K13" s="59">
-        <f>SUM(E13:J13)*C13*160</f>
+      <c r="K13" s="47">
+        <f t="shared" si="0"/>
         <v>288000</v>
       </c>
-      <c r="L13" s="58">
+      <c r="L13" s="46">
         <v>80</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57600</v>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="J14" s="10">
         <v>2</v>
       </c>
-      <c r="K14" s="59">
-        <f>SUM(E14:J14)*C14*160</f>
+      <c r="K14" s="47">
+        <f t="shared" si="0"/>
         <v>57600</v>
       </c>
-      <c r="L14" s="58">
+      <c r="L14" s="46">
         <v>80</v>
       </c>
-      <c r="M14" s="69">
-        <f t="shared" si="0"/>
+      <c r="M14" s="57">
+        <f t="shared" si="1"/>
         <v>11520</v>
       </c>
     </row>
@@ -5614,11 +5614,11 @@
       <c r="J15" s="8">
         <v>16</v>
       </c>
-      <c r="K15" s="62">
-        <f>SUM(E15:J15)*C15*160</f>
+      <c r="K15" s="50">
+        <f t="shared" si="0"/>
         <v>264000</v>
       </c>
-      <c r="L15" s="63">
+      <c r="L15" s="51">
         <v>80</v>
       </c>
       <c r="M15" s="13">
@@ -5627,51 +5627,51 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31">
-        <f>SUM(E3:E15)</f>
+      <c r="B16" s="125"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="26">
+        <f t="shared" ref="E16:K16" si="2">SUM(E3:E15)</f>
         <v>40</v>
       </c>
-      <c r="F16" s="31">
-        <f>SUM(F3:F15)</f>
+      <c r="F16" s="26">
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="G16" s="31">
-        <f>SUM(G3:G15)</f>
+      <c r="G16" s="26">
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="H16" s="31">
-        <f>SUM(H3:H15)</f>
+      <c r="H16" s="26">
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="I16" s="31">
-        <f>SUM(I3:I15)</f>
+      <c r="I16" s="26">
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="J16" s="43">
-        <f>SUM(J3:J15)</f>
+      <c r="J16" s="32">
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="K16" s="65">
-        <f>SUM(K3:K15)</f>
+      <c r="K16" s="53">
+        <f t="shared" si="2"/>
         <v>2568000</v>
       </c>
-      <c r="L16" s="70"/>
-      <c r="M16" s="67">
+      <c r="L16" s="58"/>
+      <c r="M16" s="55">
         <f>SUM(M3:M15)</f>
         <v>513600</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="35"/>
+      <c r="C17" s="122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="122"/>
       <c r="E17" s="18">
         <v>46569</v>
       </c>
@@ -5690,180 +5690,180 @@
       <c r="J17" s="18">
         <v>46722</v>
       </c>
-      <c r="K17" s="45" t="s">
+      <c r="K17" s="33" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="53">
+      <c r="C18" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="150"/>
+      <c r="E18" s="41">
         <v>600</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="41">
         <v>600</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="41">
         <v>600</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="41">
         <v>600</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="41">
         <v>600</v>
       </c>
-      <c r="J18" s="53">
+      <c r="J18" s="41">
         <v>600</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="42">
         <f>SUM(E18:J18)</f>
         <v>3600</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="53">
+      <c r="D19" s="151"/>
+      <c r="E19" s="41">
         <v>600</v>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="41">
         <v>600</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="41">
         <v>600</v>
       </c>
-      <c r="H19" s="53">
+      <c r="H19" s="41">
         <v>600</v>
       </c>
-      <c r="I19" s="53">
+      <c r="I19" s="41">
         <v>600</v>
       </c>
-      <c r="J19" s="53">
+      <c r="J19" s="41">
         <v>600</v>
       </c>
-      <c r="K19" s="57">
+      <c r="K19" s="45">
         <f>SUM(E19:J19)</f>
         <v>3600</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="56">
+      <c r="C20" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="151"/>
+      <c r="E20" s="44">
         <v>5000</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="44">
         <v>5000</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="44">
         <v>5000</v>
       </c>
-      <c r="H20" s="56">
+      <c r="H20" s="44">
         <v>5000</v>
       </c>
-      <c r="I20" s="56">
+      <c r="I20" s="44">
         <v>5000</v>
       </c>
-      <c r="J20" s="56">
+      <c r="J20" s="44">
         <v>5000</v>
       </c>
-      <c r="K20" s="57">
+      <c r="K20" s="45">
         <f>SUM(E20:J20)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="76" t="s">
+      <c r="C21" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="76"/>
-      <c r="E21" s="61">
+      <c r="D21" s="152"/>
+      <c r="E21" s="49">
         <v>5000</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="49">
         <v>5000</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="49">
         <v>5000</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="49">
         <v>5000</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="49">
         <v>5000</v>
       </c>
-      <c r="J21" s="61">
+      <c r="J21" s="49">
         <v>5000</v>
       </c>
-      <c r="K21" s="62">
+      <c r="K21" s="50">
         <f>SUM(E21:J21)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="64">
+      <c r="B22" s="145"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="52">
         <f>SUM(E18:E21)</f>
         <v>11200</v>
       </c>
-      <c r="F22" s="64">
-        <f t="shared" ref="F22:J22" si="1">SUM(F18:F21)</f>
+      <c r="F22" s="52">
+        <f t="shared" ref="F22:J22" si="3">SUM(F18:F21)</f>
         <v>11200</v>
       </c>
-      <c r="G22" s="64">
-        <f t="shared" si="1"/>
+      <c r="G22" s="52">
+        <f t="shared" si="3"/>
         <v>11200</v>
       </c>
-      <c r="H22" s="64">
-        <f t="shared" si="1"/>
+      <c r="H22" s="52">
+        <f t="shared" si="3"/>
         <v>11200</v>
       </c>
-      <c r="I22" s="64">
-        <f t="shared" si="1"/>
+      <c r="I22" s="52">
+        <f t="shared" si="3"/>
         <v>11200</v>
       </c>
-      <c r="J22" s="64">
-        <f t="shared" si="1"/>
+      <c r="J22" s="52">
+        <f t="shared" si="3"/>
         <v>11200</v>
       </c>
-      <c r="K22" s="65">
+      <c r="K22" s="53">
         <f>SUM(K18:K21)</f>
         <v>67200</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="66">
+      <c r="C23" s="148"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="149"/>
+      <c r="K23" s="54">
         <f>M16+K22</f>
         <v>580800</v>
       </c>
